--- a/docs/buildx_build_and_push_guide.xlsx
+++ b/docs/buildx_build_and_push_guide.xlsx
@@ -285,7 +285,7 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-05 05:22:05</t>
+          <t xml:space="preserve">2026-08-05 06:13:17</t>
         </is>
       </c>
     </row>

--- a/docs/buildx_build_and_push_guide.xlsx
+++ b/docs/buildx_build_and_push_guide.xlsx
@@ -285,7 +285,7 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-05 06:13:17</t>
+          <t xml:space="preserve">2026-08-05 10:03:50</t>
         </is>
       </c>
     </row>
@@ -1239,7 +1239,7 @@
         </is>
       </c>
     </row>
-    <row r="58" ht="82.5" customHeight="1">
+    <row r="58" ht="181.5" customHeight="1">
       <c r="A58" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">18</t>
@@ -1252,7 +1252,7 @@
       </c>
       <c r="C58" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">docker buildx build --load -t &lt;local-image&gt; -f &lt;dockerfile&gt; [オプション] &lt;context&gt;</t>
+          <t xml:space="preserve">docker buildx build --load -t &lt;local-image&gt; -f &lt;dockerfile&gt; [オプション] &lt;context&gt; を監視プロセス付きで実行 (進捗表示・停滞検知・上限時間での中断。6.8 参照)。開始前に data root の空き容量を確認</t>
         </is>
       </c>
       <c r="D58" s="3" t="inlineStr">
@@ -1766,7 +1766,7 @@
         </is>
       </c>
     </row>
-    <row r="96" ht="231.0" customHeight="1">
+    <row r="96" ht="264.0" customHeight="1">
       <c r="A96" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
@@ -1779,11 +1779,11 @@
       </c>
       <c r="C96" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">AWS 未認証、buildx 不在、Docker デーモン未接続、ECR 権限なし、スイッチバック失敗、SSM 取得失敗、コピー失敗、Dockerfile / コンテキスト不在、ビルド失敗、ローカルイメージ未検出、ログイン失敗、タグ付け失敗、push 失敗、出力書き込み失敗、ログディレクトリ作成失敗</t>
-        </is>
-      </c>
-    </row>
-    <row r="97" ht="198.0" customHeight="1">
+          <t xml:space="preserve">AWS 未認証、buildx 不在、Docker デーモン未接続、ECR 権限なし、スイッチバック失敗、SSM 取得失敗、コピー失敗、Dockerfile / コンテキスト不在、ビルド失敗、--build-timeout の上限超過によるビルド中断、ローカルイメージ未検出、ログイン失敗、タグ付け失敗、push 失敗、出力書き込み失敗、ログディレクトリ作成失敗</t>
+        </is>
+      </c>
+    </row>
+    <row r="97" ht="214.5" customHeight="1">
       <c r="A97" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C97" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">不明なオプション、値の欠落、--account-id/--registry 未指定、複数 platform 指定、--progress の不正値、リポジトリ名・タグ接頭辞の形式違反、JBoss オプションの排他違反、--jboss-secret-id が空、--copy-file の書式不正</t>
+          <t xml:space="preserve">不明なオプション、値の欠落、ビルド監視の各値が 0 未満か非数値、--account-id/--registry 未指定、複数 platform 指定、--progress の不正値、リポジトリ名・タグ接頭辞の形式違反、JBoss オプションの排他違反、--jboss-secret-id が空、--copy-file の書式不正</t>
         </is>
       </c>
     </row>
@@ -2567,7 +2567,7 @@
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">CI ログには plain が読みやすい</t>
+          <t xml:space="preserve">CI ログには plain が読みやすい。ビルド監視が有効な間は tty を plain へ切り替える</t>
         </is>
       </c>
     </row>
@@ -2603,99 +2603,111 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="19.5" customHeight="1">
+    <row r="20" ht="33.0" customHeight="1">
       <c r="A20" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.3 出力・実行制御</t>
+          <t xml:space="preserve">5.2 buildx ビルド関連 (このスクリプト固有)</t>
         </is>
       </c>
       <c r="B20" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--container-name NAME</t>
+          <t xml:space="preserve">--build-progress-interval SEC</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">任意の文字列</t>
+          <t xml:space="preserve">0 以上の整数 (秒)</t>
         </is>
       </c>
       <c r="D20" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">--repository の値</t>
-        </is>
-      </c>
-      <c r="E20" s="7"/>
+          <t xml:space="preserve">30</t>
+        </is>
+      </c>
+      <c r="E20" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不可</t>
+        </is>
+      </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">imagedefinition.json の name</t>
+          <t xml:space="preserve">ビルド中に経過時間・BuildKit のフェーズ・data root の空き容量の増減を表示する間隔。0 で表示しない</t>
         </is>
       </c>
     </row>
     <row r="21" ht="33.0" customHeight="1">
       <c r="A21" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.3 出力・実行制御</t>
+          <t xml:space="preserve">5.2 buildx ビルド関連 (このスクリプト固有)</t>
         </is>
       </c>
       <c r="B21" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--output FILE</t>
+          <t xml:space="preserve">--build-stall-timeout SEC</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ファイルパス</t>
+          <t xml:space="preserve">0 以上の整数 (秒)</t>
         </is>
       </c>
       <c r="D21" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">imagedefinition.json</t>
-        </is>
-      </c>
-      <c r="E21" s="7"/>
+          <t xml:space="preserve">300</t>
+        </is>
+      </c>
+      <c r="E21" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不可</t>
+        </is>
+      </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">imagedefinition の出力先</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="19.5" customHeight="1">
+          <t xml:space="preserve">ビルド出力がこの秒数途切れたら停滞と判断し、原因の切り分け診断を表示する。0 で検知しない。検知しても処理は中断しない</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="33.0" customHeight="1">
       <c r="A22" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.3 出力・実行制御</t>
+          <t xml:space="preserve">5.2 buildx ビルド関連 (このスクリプト固有)</t>
         </is>
       </c>
       <c r="B22" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--log-dir DIR</t>
+          <t xml:space="preserve">--build-timeout SEC</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ディレクトリパス</t>
-        </is>
-      </c>
-      <c r="D22" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(なし)</t>
-        </is>
-      </c>
-      <c r="E22" s="7"/>
+          <t xml:space="preserve">0 以上の整数 (秒)</t>
+        </is>
+      </c>
+      <c r="D22" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0 (無制限)</t>
+        </is>
+      </c>
+      <c r="E22" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不可</t>
+        </is>
+      </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">画面出力を DIR/buildx_build_and_push_&lt;日時&gt;.log にも保存</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="19.5" customHeight="1">
+          <t xml:space="preserve">ビルド全体の上限秒数。超えたら診断のうえ SIGTERM で中断し (20 秒後に SIGKILL)、exit 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="33.0" customHeight="1">
       <c r="A23" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.3 出力・実行制御</t>
+          <t xml:space="preserve">5.2 buildx ビルド関連 (このスクリプト固有)</t>
         </is>
       </c>
       <c r="B23" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--dry-run</t>
+          <t xml:space="preserve">--no-build-watchdog</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
@@ -2708,10 +2720,14 @@
           <t xml:space="preserve">false</t>
         </is>
       </c>
-      <c r="E23" s="7"/>
+      <c r="E23" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ビルド/ログイン/タグ付け/プッシュ/ファイル出力を行わずプレビュー</t>
+          <t xml:space="preserve">上記の監視をすべて行わない</t>
         </is>
       </c>
     </row>
@@ -2723,72 +2739,68 @@
       </c>
       <c r="B24" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">-h, --help</t>
+          <t xml:space="preserve">--container-name NAME</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">フラグ</t>
-        </is>
-      </c>
-      <c r="D24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">—</t>
+          <t xml:space="preserve">任意の文字列</t>
+        </is>
+      </c>
+      <c r="D24" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--repository の値</t>
         </is>
       </c>
       <c r="E24" s="7"/>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ヘルプを表示して exit 0</t>
+          <t xml:space="preserve">imagedefinition.json の name</t>
         </is>
       </c>
     </row>
     <row r="25" ht="33.0" customHeight="1">
       <c r="A25" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.4 ビルド前後の一時ファイル</t>
+          <t xml:space="preserve">5.3 出力・実行制御</t>
         </is>
       </c>
       <c r="B25" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--copy-file SRC:DEST_DIR</t>
+          <t xml:space="preserve">--output FILE</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">コピー元:コピー先ディレクトリ</t>
-        </is>
-      </c>
-      <c r="D25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(なし)</t>
-        </is>
-      </c>
-      <c r="E25" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">可</t>
-        </is>
-      </c>
+          <t xml:space="preserve">ファイルパス</t>
+        </is>
+      </c>
+      <c r="D25" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">imagedefinition.json</t>
+        </is>
+      </c>
+      <c r="E25" s="7"/>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ビルド前にコピーし、終了後に自動削除</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="49.5" customHeight="1">
+          <t xml:space="preserve">imagedefinition の出力先</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="19.5" customHeight="1">
       <c r="A26" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.5 JBoss マスターパスワード (BuildKit シークレット)</t>
+          <t xml:space="preserve">5.3 出力・実行制御</t>
         </is>
       </c>
       <c r="B26" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--jboss-password-param NAME</t>
+          <t xml:space="preserve">--log-dir DIR</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">SSM パラメータ名</t>
+          <t xml:space="preserve">ディレクトリパス</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
@@ -2799,180 +2811,296 @@
       <c r="E26" s="7"/>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">パラメータストアから取得 (--with-decryption)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="49.5" customHeight="1">
+          <t xml:space="preserve">画面出力を DIR/buildx_build_and_push_&lt;日時&gt;.log にも保存</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="19.5" customHeight="1">
       <c r="A27" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.5 JBoss マスターパスワード (BuildKit シークレット)</t>
+          <t xml:space="preserve">5.3 出力・実行制御</t>
         </is>
       </c>
       <c r="B27" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--jboss-password VALUE</t>
+          <t xml:space="preserve">--dry-run</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">パスワード文字列</t>
+          <t xml:space="preserve">フラグ</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">(なし)</t>
+          <t xml:space="preserve">false</t>
         </is>
       </c>
       <c r="E27" s="7"/>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">直接指定。--jboss-password-param とは排他</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="49.5" customHeight="1">
+          <t xml:space="preserve">ビルド/ログイン/タグ付け/プッシュ/ファイル出力を行わずプレビュー</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="19.5" customHeight="1">
       <c r="A28" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.5 JBoss マスターパスワード (BuildKit シークレット)</t>
+          <t xml:space="preserve">5.3 出力・実行制御</t>
         </is>
       </c>
       <c r="B28" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--jboss-password-env NAME</t>
+          <t xml:space="preserve">-h, --help</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">環境変数名</t>
-        </is>
-      </c>
-      <c r="D28" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">JBOSS_MASTER_PASSWORD</t>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
         </is>
       </c>
       <c r="E28" s="7"/>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">受け渡しに使う環境変数名</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="49.5" customHeight="1">
+          <t xml:space="preserve">ヘルプを表示して exit 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="33.0" customHeight="1">
       <c r="A29" s="11" t="inlineStr">
         <is>
+          <t xml:space="preserve">5.4 ビルド前後の一時ファイル</t>
+        </is>
+      </c>
+      <c r="B29" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--copy-file SRC:DEST_DIR</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">コピー元:コピー先ディレクトリ</t>
+        </is>
+      </c>
+      <c r="D29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(なし)</t>
+        </is>
+      </c>
+      <c r="E29" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">可</t>
+        </is>
+      </c>
+      <c r="F29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ビルド前にコピーし、終了後に自動削除</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="49.5" customHeight="1">
+      <c r="A30" s="11" t="inlineStr">
+        <is>
           <t xml:space="preserve">5.5 JBoss マスターパスワード (BuildKit シークレット)</t>
         </is>
       </c>
-      <c r="B29" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--jboss-secret-id ID</t>
-        </is>
-      </c>
-      <c r="C29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">シークレット id</t>
-        </is>
-      </c>
-      <c r="D29" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">jboss_master_password</t>
-        </is>
-      </c>
-      <c r="E29" s="7"/>
-      <c r="F29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">--secret id=... の id。Dockerfile の RUN --mount=type=secret,id=... と一致させる</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="33.0" customHeight="1">
-      <c r="A30" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5.6 スイッチバック</t>
-        </is>
-      </c>
       <c r="B30" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--switchback-shell PATH</t>
+          <t xml:space="preserve">--jboss-password-param NAME</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">シェルスクリプトのパス</t>
-        </is>
-      </c>
-      <c r="D30" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">env SWITCHBACK_SHELL</t>
+          <t xml:space="preserve">SSM パラメータ名</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(なし)</t>
         </is>
       </c>
       <c r="E30" s="7"/>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">スイッチバック用シェル (source で読み込む)</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="19.5" customHeight="1">
+          <t xml:space="preserve">パラメータストアから取得 (--with-decryption)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="49.5" customHeight="1">
       <c r="A31" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.6 スイッチバック</t>
+          <t xml:space="preserve">5.5 JBoss マスターパスワード (BuildKit シークレット)</t>
         </is>
       </c>
       <c r="B31" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--auto-switchback</t>
+          <t xml:space="preserve">--jboss-password VALUE</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">フラグ</t>
+          <t xml:space="preserve">パスワード文字列</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">false</t>
+          <t xml:space="preserve">(なし)</t>
         </is>
       </c>
       <c r="E31" s="7"/>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ECR 権限が無い場合に自動でスイッチバックして継続</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="19.5" customHeight="1">
+          <t xml:space="preserve">直接指定。--jboss-password-param とは排他</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="49.5" customHeight="1">
       <c r="A32" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.6 スイッチバック</t>
+          <t xml:space="preserve">5.5 JBoss マスターパスワード (BuildKit シークレット)</t>
         </is>
       </c>
       <c r="B32" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--warn-only</t>
+          <t xml:space="preserve">--jboss-password-env NAME</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">フラグ</t>
+          <t xml:space="preserve">環境変数名</t>
         </is>
       </c>
       <c r="D32" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">既定</t>
+          <t xml:space="preserve">JBOSS_MASTER_PASSWORD</t>
         </is>
       </c>
       <c r="E32" s="7"/>
       <c r="F32" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">受け渡しに使う環境変数名</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="49.5" customHeight="1">
+      <c r="A33" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.5 JBoss マスターパスワード (BuildKit シークレット)</t>
+        </is>
+      </c>
+      <c r="B33" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--jboss-secret-id ID</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">シークレット id</t>
+        </is>
+      </c>
+      <c r="D33" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">jboss_master_password</t>
+        </is>
+      </c>
+      <c r="E33" s="7"/>
+      <c r="F33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--secret id=... の id。Dockerfile の RUN --mount=type=secret,id=... と一致させる</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="33.0" customHeight="1">
+      <c r="A34" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.6 スイッチバック</t>
+        </is>
+      </c>
+      <c r="B34" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--switchback-shell PATH</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">シェルスクリプトのパス</t>
+        </is>
+      </c>
+      <c r="D34" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">env SWITCHBACK_SHELL</t>
+        </is>
+      </c>
+      <c r="E34" s="7"/>
+      <c r="F34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">スイッチバック用シェル (source で読み込む)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="19.5" customHeight="1">
+      <c r="A35" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.6 スイッチバック</t>
+        </is>
+      </c>
+      <c r="B35" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--auto-switchback</t>
+        </is>
+      </c>
+      <c r="C35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+      <c r="E35" s="7"/>
+      <c r="F35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ECR 権限が無い場合に自動でスイッチバックして継続</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="19.5" customHeight="1">
+      <c r="A36" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.6 スイッチバック</t>
+        </is>
+      </c>
+      <c r="B36" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--warn-only</t>
+        </is>
+      </c>
+      <c r="C36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">フラグ</t>
+        </is>
+      </c>
+      <c r="D36" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">既定</t>
+        </is>
+      </c>
+      <c r="E36" s="7"/>
+      <c r="F36" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">ECR 権限が無い場合に警告して終了</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:F32"/>
+  <autoFilter ref="A4:F36"/>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A2:F2"/>
@@ -3262,266 +3390,332 @@
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">CI ログには plain が読みやすい</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="19.5" customHeight="1">
+          <t xml:space="preserve">CI ログには plain が読みやすい。ビルド監視が有効な間は tty を plain へ切り替える</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="33.0" customHeight="1">
       <c r="A16" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.3 出力・実行制御</t>
+          <t xml:space="preserve">5.2 buildx ビルド関連 (このスクリプト固有)</t>
         </is>
       </c>
       <c r="B16" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--container-name NAME</t>
+          <t xml:space="preserve">--build-progress-interval SEC</t>
         </is>
       </c>
       <c r="C16" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">--repository の値</t>
+          <t xml:space="preserve">30</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">imagedefinition.json の name</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="19.5" customHeight="1">
+          <t xml:space="preserve">ビルド中に経過時間・BuildKit のフェーズ・data root の空き容量の増減を表示する間隔。0 で表示しない</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="33.0" customHeight="1">
       <c r="A17" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.3 出力・実行制御</t>
+          <t xml:space="preserve">5.2 buildx ビルド関連 (このスクリプト固有)</t>
         </is>
       </c>
       <c r="B17" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--output FILE</t>
+          <t xml:space="preserve">--build-stall-timeout SEC</t>
         </is>
       </c>
       <c r="C17" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">imagedefinition.json</t>
+          <t xml:space="preserve">300</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">imagedefinition の出力先</t>
+          <t xml:space="preserve">ビルド出力がこの秒数途切れたら停滞と判断し、原因の切り分け診断を表示する。0 で検知しない。検知しても処理は中断しない</t>
         </is>
       </c>
     </row>
     <row r="18" ht="33.0" customHeight="1">
       <c r="A18" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.5 JBoss マスターパスワード (BuildKit シークレット)</t>
+          <t xml:space="preserve">5.2 buildx ビルド関連 (このスクリプト固有)</t>
         </is>
       </c>
       <c r="B18" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--jboss-password-env NAME</t>
+          <t xml:space="preserve">--build-timeout SEC</t>
         </is>
       </c>
       <c r="C18" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">JBOSS_MASTER_PASSWORD</t>
+          <t xml:space="preserve">0 (無制限)</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">受け渡しに使う環境変数名</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="33.0" customHeight="1">
+          <t xml:space="preserve">ビルド全体の上限秒数。超えたら診断のうえ SIGTERM で中断し (20 秒後に SIGKILL)、exit 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="19.5" customHeight="1">
       <c r="A19" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.5 JBoss マスターパスワード (BuildKit シークレット)</t>
+          <t xml:space="preserve">5.3 出力・実行制御</t>
         </is>
       </c>
       <c r="B19" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">--jboss-secret-id ID</t>
+          <t xml:space="preserve">--container-name NAME</t>
         </is>
       </c>
       <c r="C19" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">jboss_master_password</t>
+          <t xml:space="preserve">--repository の値</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">--secret id=... の id。Dockerfile の RUN --mount=type=secret,id=... と一致させる</t>
+          <t xml:space="preserve">imagedefinition.json の name</t>
         </is>
       </c>
     </row>
     <row r="20" ht="19.5" customHeight="1">
       <c r="A20" s="11" t="inlineStr">
         <is>
+          <t xml:space="preserve">5.3 出力・実行制御</t>
+        </is>
+      </c>
+      <c r="B20" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--output FILE</t>
+        </is>
+      </c>
+      <c r="C20" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">imagedefinition.json</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">imagedefinition の出力先</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="33.0" customHeight="1">
+      <c r="A21" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.5 JBoss マスターパスワード (BuildKit シークレット)</t>
+        </is>
+      </c>
+      <c r="B21" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--jboss-password-env NAME</t>
+        </is>
+      </c>
+      <c r="C21" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">JBOSS_MASTER_PASSWORD</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">受け渡しに使う環境変数名</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="33.0" customHeight="1">
+      <c r="A22" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.5 JBoss マスターパスワード (BuildKit シークレット)</t>
+        </is>
+      </c>
+      <c r="B22" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--jboss-secret-id ID</t>
+        </is>
+      </c>
+      <c r="C22" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">jboss_master_password</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--secret id=... の id。Dockerfile の RUN --mount=type=secret,id=... と一致させる</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="19.5" customHeight="1">
+      <c r="A23" s="11" t="inlineStr">
+        <is>
           <t xml:space="preserve">5.6 スイッチバック</t>
         </is>
       </c>
-      <c r="B20" s="11" t="inlineStr">
+      <c r="B23" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">--switchback-shell PATH</t>
         </is>
       </c>
-      <c r="C20" s="10" t="inlineStr">
+      <c r="C23" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">env SWITCHBACK_SHELL</t>
         </is>
       </c>
-      <c r="D20" s="3" t="inlineStr">
+      <c r="D23" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">スイッチバック用シェル (source で読み込む)</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="19.5" customHeight="1">
-      <c r="A21" s="11" t="inlineStr">
+    <row r="24" ht="19.5" customHeight="1">
+      <c r="A24" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">5.6 スイッチバック</t>
         </is>
       </c>
-      <c r="B21" s="11" t="inlineStr">
+      <c r="B24" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">--warn-only</t>
         </is>
       </c>
-      <c r="C21" s="10" t="inlineStr">
+      <c r="C24" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">既定</t>
         </is>
       </c>
-      <c r="D21" s="3" t="inlineStr">
+      <c r="D24" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">ECR 権限が無い場合に警告して終了</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="9.0" customHeight="1">
-      <c r="A22" s="0"/>
-    </row>
-    <row r="23" ht="24.0" customHeight="1">
-      <c r="A23" s="5" t="inlineStr">
+    <row r="25" ht="9.0" customHeight="1">
+      <c r="A25" s="0"/>
+    </row>
+    <row r="26" ht="24.0" customHeight="1">
+      <c r="A26" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">その他、既定の挙動として説明されている項目</t>
         </is>
       </c>
-      <c r="B23" s="5"/>
-      <c r="C23" s="5"/>
-      <c r="D23" s="5"/>
-    </row>
-    <row r="24" ht="19.5" customHeight="1">
-      <c r="A24" s="2" t="inlineStr">
+      <c r="B26" s="5"/>
+      <c r="C26" s="5"/>
+      <c r="D26" s="5"/>
+    </row>
+    <row r="27" ht="19.5" customHeight="1">
+      <c r="A27" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">記載箇所</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
+      <c r="B27" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">内容</t>
         </is>
       </c>
-      <c r="C24" s="2"/>
-      <c r="D24" s="2"/>
-    </row>
-    <row r="25" ht="19.5" customHeight="1">
-      <c r="A25" s="11" t="inlineStr">
+      <c r="C27" s="2"/>
+      <c r="D27" s="2"/>
+    </row>
+    <row r="28" ht="19.5" customHeight="1">
+      <c r="A28" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">前提条件</t>
         </is>
       </c>
-      <c r="B25" s="3" t="inlineStr">
+      <c r="B28" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">権限が無い場合 / 既定は警告して終了 (--warn-only)。--auto-switchback で自動スイッチバック</t>
-        </is>
-      </c>
-      <c r="C25" s="3"/>
-      <c r="D25" s="3"/>
-    </row>
-    <row r="26" ht="19.5" customHeight="1">
-      <c r="A26" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">compose 版との違い</t>
-        </is>
-      </c>
-      <c r="B26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">進捗表示形式 / BuildKit 既定 / --progress</t>
-        </is>
-      </c>
-      <c r="C26" s="3"/>
-      <c r="D26" s="3"/>
-    </row>
-    <row r="27" ht="33.0" customHeight="1">
-      <c r="A27" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3.1 ファイル内のセクション構成</t>
-        </is>
-      </c>
-      <c r="B27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">前半 / 既定値 / 全パラメータの初期値</t>
-        </is>
-      </c>
-      <c r="C27" s="3"/>
-      <c r="D27" s="3"/>
-    </row>
-    <row r="28" ht="33.0" customHeight="1">
-      <c r="A28" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">6.3 --secret と --jboss-secret-id の関係</t>
-        </is>
-      </c>
-      <c r="B28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">JBoss マスターパスワード / --jboss-password-param などで有効化 / --jboss-secret-id (既定 jboss_master_password)</t>
         </is>
       </c>
       <c r="C28" s="3"/>
       <c r="D28" s="3"/>
     </row>
-    <row r="29" ht="33.0" customHeight="1">
+    <row r="29" ht="19.5" customHeight="1">
       <c r="A29" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">7.1 入力として参照する環境変数</t>
+          <t xml:space="preserve">compose 版との違い</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">JBOSS_MASTER_PASSWORD (既定名) / --jboss-password-env / 事前 export した値をそのまま使用</t>
+          <t xml:space="preserve">進捗表示形式 / BuildKit 既定 / --progress</t>
         </is>
       </c>
       <c r="C29" s="3"/>
       <c r="D29" s="3"/>
     </row>
-    <row r="30" ht="19.5" customHeight="1">
+    <row r="30" ht="33.0" customHeight="1">
       <c r="A30" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">入出力ファイル</t>
+          <t xml:space="preserve">3.1 ファイル内のセクション構成</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力 / ビルドコンテキスト (--context) / 既定はカレントディレクトリ</t>
+          <t xml:space="preserve">前半 / 既定値 / 全パラメータの初期値</t>
         </is>
       </c>
       <c r="C30" s="3"/>
       <c r="D30" s="3"/>
+    </row>
+    <row r="31" ht="33.0" customHeight="1">
+      <c r="A31" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6.3 --secret と --jboss-secret-id の関係</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">JBoss マスターパスワード / --jboss-password-param などで有効化 / --jboss-secret-id (既定 jboss_master_password)</t>
+        </is>
+      </c>
+      <c r="C31" s="3"/>
+      <c r="D31" s="3"/>
+    </row>
+    <row r="32" ht="33.0" customHeight="1">
+      <c r="A32" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7.1 入力として参照する環境変数</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">JBOSS_MASTER_PASSWORD (既定名) / --jboss-password-env / 事前 export した値をそのまま使用</t>
+        </is>
+      </c>
+      <c r="C32" s="3"/>
+      <c r="D32" s="3"/>
+    </row>
+    <row r="33" ht="19.5" customHeight="1">
+      <c r="A33" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入出力ファイル</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力 / ビルドコンテキスト (--context) / 既定はカレントディレクトリ</t>
+        </is>
+      </c>
+      <c r="C33" s="3"/>
+      <c r="D33" s="3"/>
     </row>
   </sheetData>
   <mergeCells count="11">
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A2:D2"/>
     <mergeCell ref="A4:D4"/>
-    <mergeCell ref="A23:D23"/>
-    <mergeCell ref="B24:D24"/>
-    <mergeCell ref="B25:D25"/>
-    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="A26:D26"/>
     <mergeCell ref="B27:D27"/>
     <mergeCell ref="B28:D28"/>
     <mergeCell ref="B29:D29"/>
     <mergeCell ref="B30:D30"/>
+    <mergeCell ref="B31:D31"/>
+    <mergeCell ref="B32:D32"/>
+    <mergeCell ref="B33:D33"/>
   </mergeCells>
   <pageMargins left="0.5" right="0.5" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3702,7 +3896,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="49.5" customHeight="1">
+    <row r="12" ht="99.0" customHeight="1">
       <c r="A12" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">8</t>
@@ -3710,14 +3904,19 @@
       </c>
       <c r="B12" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">ECR 権限が無い場合に自動スイッチバック + ログ保存</t>
+          <t xml:space="preserve">ECR 権限が無い場合に自動スイッチバック + ログ保存
+ビルドが exporting layers から進まないときの調査 (進捗 10 秒 / 停滞判定 60 秒)
+30 分を超えたらビルドを中断して確実にプロンプトを戻す</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">./buildx_build_and_push.sh --account-id 123456789012 \
     --auto-switchback --switchback-shell /opt/team/switchback.sh \
-    --log-dir ./logs</t>
+    --log-dir ./logs
+./buildx_build_and_push.sh --account-id 123456789012 \
+    --build-progress-interval 10 --build-stall-timeout 60
+./buildx_build_and_push.sh --account-id 123456789012 --build-timeout 1800</t>
         </is>
       </c>
     </row>

--- a/docs/buildx_build_and_push_guide.xlsx
+++ b/docs/buildx_build_and_push_guide.xlsx
@@ -285,7 +285,7 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-05 10:03:50</t>
+          <t xml:space="preserve">2026-08-11 15:06:08</t>
         </is>
       </c>
     </row>

--- a/docs/buildx_build_and_push_guide.xlsx
+++ b/docs/buildx_build_and_push_guide.xlsx
@@ -285,7 +285,7 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-11 15:06:08</t>
+          <t xml:space="preserve">2026-08-12 13:21:33</t>
         </is>
       </c>
     </row>
@@ -1403,7 +1403,7 @@
       </c>
       <c r="B67" s="8"/>
     </row>
-    <row r="68" ht="181.5" customHeight="1">
+    <row r="68" ht="198.0" customHeight="1">
       <c r="A68" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">docker buildx build \
@@ -1416,6 +1416,7 @@
   [--build-context NAME=VALUE ...] \
   [--secret &lt;SPEC&gt; ...] \
   [--secret id=&lt;JBOSS_SECRET_ID&gt;,env=&lt;JBOSS_PASSWORD_ENV&gt;] \
+  [--secret id=&lt;CACERT_SECRET_ID&gt;,src=&lt;生成した tar&gt;] \
   &lt;BUILD_CONTEXT&gt;</t>
         </is>
       </c>
@@ -1433,9 +1434,9 @@
       <c r="A70" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">・--load は常に付与されます (docker image tag / docker image push を使うため)
-・JBoss シークレットは --secret の最後に追加されます
-・--secret の引数に含まれるのは id と環境変数名のみで、パスワードの値は含まれません
-  (--dry-run のプレビューにも値は出ません)</t>
+・JBoss シークレットと CA 証明書シークレットは --secret の最後にこの順で追加されます
+・--secret の引数に含まれるのは id と環境変数名 (JBoss) / tar のパス (CA 証明書) のみで、
+  パスワードの値は含まれません (--dry-run のプレビューにも値は出ません)</t>
         </is>
       </c>
       <c r="B70" s="3"/>
@@ -3099,8 +3100,128 @@
         </is>
       </c>
     </row>
+    <row r="37" ht="33.0" customHeight="1">
+      <c r="A37" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.7 CA 証明書 (BuildKit シークレット)</t>
+        </is>
+      </c>
+      <c r="B37" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--cacert-dir DIR</t>
+        </is>
+      </c>
+      <c r="C37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ディレクトリのパス</t>
+        </is>
+      </c>
+      <c r="D37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(なし)</t>
+        </is>
+      </c>
+      <c r="E37" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">可</t>
+        </is>
+      </c>
+      <c r="F37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cacert.crt を置いたディレクトリ。指定した全ディレクトリ分を 1 つの tar にまとめて --secret で渡す</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="33.0" customHeight="1">
+      <c r="A38" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.7 CA 証明書 (BuildKit シークレット)</t>
+        </is>
+      </c>
+      <c r="B38" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--cacert-secret-id ID</t>
+        </is>
+      </c>
+      <c r="C38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">英数字と . _ -</t>
+        </is>
+      </c>
+      <c r="D38" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cacerts</t>
+        </is>
+      </c>
+      <c r="E38" s="7"/>
+      <c r="F38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">シークレット id。Dockerfile の RUN --mount=type=secret,id=... と一致させる</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="33.0" customHeight="1">
+      <c r="A39" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.7 CA 証明書 (BuildKit シークレット)</t>
+        </is>
+      </c>
+      <c r="B39" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--cacert-bundle PATH</t>
+        </is>
+      </c>
+      <c r="C39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tar のパス</t>
+        </is>
+      </c>
+      <c r="D39" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">一時ファイル</t>
+        </is>
+      </c>
+      <c r="E39" s="7"/>
+      <c r="F39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">生成する tar の出力先。指定時は自動削除しない</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="33.0" customHeight="1">
+      <c r="A40" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.7 CA 証明書 (BuildKit シークレット)</t>
+        </is>
+      </c>
+      <c r="B40" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--cacert-glob PATTERN</t>
+        </is>
+      </c>
+      <c r="C40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">glob パターン</t>
+        </is>
+      </c>
+      <c r="D40" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">*.crt と *.pem</t>
+        </is>
+      </c>
+      <c r="E40" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">可</t>
+        </is>
+      </c>
+      <c r="F40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">各ディレクトリから取り込むファイルのパターン。指定するとこの値だけが対象になる</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A4:F36"/>
+  <autoFilter ref="A4:F40"/>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A2:F2"/>
@@ -3592,130 +3713,196 @@
         </is>
       </c>
     </row>
-    <row r="25" ht="9.0" customHeight="1">
-      <c r="A25" s="0"/>
-    </row>
-    <row r="26" ht="24.0" customHeight="1">
-      <c r="A26" s="5" t="inlineStr">
+    <row r="25" ht="33.0" customHeight="1">
+      <c r="A25" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.7 CA 証明書 (BuildKit シークレット)</t>
+        </is>
+      </c>
+      <c r="B25" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--cacert-secret-id ID</t>
+        </is>
+      </c>
+      <c r="C25" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cacerts</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">シークレット id。Dockerfile の RUN --mount=type=secret,id=... と一致させる</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="33.0" customHeight="1">
+      <c r="A26" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.7 CA 証明書 (BuildKit シークレット)</t>
+        </is>
+      </c>
+      <c r="B26" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--cacert-bundle PATH</t>
+        </is>
+      </c>
+      <c r="C26" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">一時ファイル</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">生成する tar の出力先。指定時は自動削除しない</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="33.0" customHeight="1">
+      <c r="A27" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.7 CA 証明書 (BuildKit シークレット)</t>
+        </is>
+      </c>
+      <c r="B27" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">--cacert-glob PATTERN</t>
+        </is>
+      </c>
+      <c r="C27" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">*.crt と *.pem</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">各ディレクトリから取り込むファイルのパターン。指定するとこの値だけが対象になる</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="9.0" customHeight="1">
+      <c r="A28" s="0"/>
+    </row>
+    <row r="29" ht="24.0" customHeight="1">
+      <c r="A29" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">その他、既定の挙動として説明されている項目</t>
         </is>
       </c>
-      <c r="B26" s="5"/>
-      <c r="C26" s="5"/>
-      <c r="D26" s="5"/>
-    </row>
-    <row r="27" ht="19.5" customHeight="1">
-      <c r="A27" s="2" t="inlineStr">
+      <c r="B29" s="5"/>
+      <c r="C29" s="5"/>
+      <c r="D29" s="5"/>
+    </row>
+    <row r="30" ht="19.5" customHeight="1">
+      <c r="A30" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">記載箇所</t>
         </is>
       </c>
-      <c r="B27" s="2" t="inlineStr">
+      <c r="B30" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">内容</t>
         </is>
       </c>
-      <c r="C27" s="2"/>
-      <c r="D27" s="2"/>
-    </row>
-    <row r="28" ht="19.5" customHeight="1">
-      <c r="A28" s="11" t="inlineStr">
+      <c r="C30" s="2"/>
+      <c r="D30" s="2"/>
+    </row>
+    <row r="31" ht="19.5" customHeight="1">
+      <c r="A31" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">前提条件</t>
         </is>
       </c>
-      <c r="B28" s="3" t="inlineStr">
+      <c r="B31" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">権限が無い場合 / 既定は警告して終了 (--warn-only)。--auto-switchback で自動スイッチバック</t>
-        </is>
-      </c>
-      <c r="C28" s="3"/>
-      <c r="D28" s="3"/>
-    </row>
-    <row r="29" ht="19.5" customHeight="1">
-      <c r="A29" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">compose 版との違い</t>
-        </is>
-      </c>
-      <c r="B29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">進捗表示形式 / BuildKit 既定 / --progress</t>
-        </is>
-      </c>
-      <c r="C29" s="3"/>
-      <c r="D29" s="3"/>
-    </row>
-    <row r="30" ht="33.0" customHeight="1">
-      <c r="A30" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3.1 ファイル内のセクション構成</t>
-        </is>
-      </c>
-      <c r="B30" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">前半 / 既定値 / 全パラメータの初期値</t>
-        </is>
-      </c>
-      <c r="C30" s="3"/>
-      <c r="D30" s="3"/>
-    </row>
-    <row r="31" ht="33.0" customHeight="1">
-      <c r="A31" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">6.3 --secret と --jboss-secret-id の関係</t>
-        </is>
-      </c>
-      <c r="B31" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">JBoss マスターパスワード / --jboss-password-param などで有効化 / --jboss-secret-id (既定 jboss_master_password)</t>
         </is>
       </c>
       <c r="C31" s="3"/>
       <c r="D31" s="3"/>
     </row>
-    <row r="32" ht="33.0" customHeight="1">
+    <row r="32" ht="19.5" customHeight="1">
       <c r="A32" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">7.1 入力として参照する環境変数</t>
+          <t xml:space="preserve">compose 版との違い</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">JBOSS_MASTER_PASSWORD (既定名) / --jboss-password-env / 事前 export した値をそのまま使用</t>
+          <t xml:space="preserve">進捗表示形式 / BuildKit 既定 / --progress</t>
         </is>
       </c>
       <c r="C32" s="3"/>
       <c r="D32" s="3"/>
     </row>
-    <row r="33" ht="19.5" customHeight="1">
+    <row r="33" ht="33.0" customHeight="1">
       <c r="A33" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">入出力ファイル</t>
+          <t xml:space="preserve">3.1 ファイル内のセクション構成</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">入力 / ビルドコンテキスト (--context) / 既定はカレントディレクトリ</t>
+          <t xml:space="preserve">前半 / 既定値 / 全パラメータの初期値</t>
         </is>
       </c>
       <c r="C33" s="3"/>
       <c r="D33" s="3"/>
+    </row>
+    <row r="34" ht="33.0" customHeight="1">
+      <c r="A34" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6.3 --secret と --jboss-secret-id の関係</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">JBoss マスターパスワード / --jboss-password-param などで有効化 / --jboss-secret-id (既定 jboss_master_password)</t>
+        </is>
+      </c>
+      <c r="C34" s="3"/>
+      <c r="D34" s="3"/>
+    </row>
+    <row r="35" ht="33.0" customHeight="1">
+      <c r="A35" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7.1 入力として参照する環境変数</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">JBOSS_MASTER_PASSWORD (既定名) / --jboss-password-env / 事前 export した値をそのまま使用</t>
+        </is>
+      </c>
+      <c r="C35" s="3"/>
+      <c r="D35" s="3"/>
+    </row>
+    <row r="36" ht="19.5" customHeight="1">
+      <c r="A36" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入出力ファイル</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力 / ビルドコンテキスト (--context) / 既定はカレントディレクトリ</t>
+        </is>
+      </c>
+      <c r="C36" s="3"/>
+      <c r="D36" s="3"/>
     </row>
   </sheetData>
   <mergeCells count="11">
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A2:D2"/>
     <mergeCell ref="A4:D4"/>
-    <mergeCell ref="A26:D26"/>
-    <mergeCell ref="B27:D27"/>
-    <mergeCell ref="B28:D28"/>
-    <mergeCell ref="B29:D29"/>
+    <mergeCell ref="A29:D29"/>
     <mergeCell ref="B30:D30"/>
     <mergeCell ref="B31:D31"/>
     <mergeCell ref="B32:D32"/>
     <mergeCell ref="B33:D33"/>
+    <mergeCell ref="B34:D34"/>
+    <mergeCell ref="B35:D35"/>
+    <mergeCell ref="B36:D36"/>
   </mergeCells>
   <pageMargins left="0.5" right="0.5" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
 </worksheet>

--- a/docs/buildx_build_and_push_guide.xlsx
+++ b/docs/buildx_build_and_push_guide.xlsx
@@ -285,7 +285,7 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-12 13:21:33</t>
+          <t xml:space="preserve">2026-08-14 20:41:49</t>
         </is>
       </c>
     </row>

--- a/docs/buildx_build_and_push_guide.xlsx
+++ b/docs/buildx_build_and_push_guide.xlsx
@@ -285,7 +285,7 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-14 20:41:49</t>
+          <t xml:space="preserve">2026-08-22 04:59:00</t>
         </is>
       </c>
     </row>
